--- a/CardiauFflachBiolegbl10.xlsx
+++ b/CardiauFflachBiolegbl10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Temp-MorgG\Documents\Bioleg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C129094-BF08-458F-947A-CA19A4BECBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6C129094-BF08-458F-947A-CA19A4BECBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4429ADAC-AA3F-4897-BC8D-04ED36A41351}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{1B76E752-6232-4CA8-AD2A-92AFA0CFE312}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{1B76E752-6232-4CA8-AD2A-92AFA0CFE312}"/>
   </bookViews>
   <sheets>
     <sheet name="1.1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="286">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -1007,7 +1007,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1614,13 +1614,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD47FBB-1337-4653-ADCF-04A3393E5F70}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.5703125" customWidth="1"/>
-    <col min="2" max="2" width="110.140625" customWidth="1"/>
+    <col min="1" max="1" width="65.54296875" customWidth="1"/>
+    <col min="2" max="2" width="110.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="26.1">
+    <row r="1" spans="1:2" ht="26" x14ac:dyDescent="0.6">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>8</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>10</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>12</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>14</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>16</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>18</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>20</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>22</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>24</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>26</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>28</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>30</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>32</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15" thickBot="1">
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16" t="s">
         <v>34</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1">
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>36</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1">
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>38</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15" thickBot="1">
+    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>40</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="29.1">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
         <v>42</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15" thickBot="1">
+    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16" t="s">
         <v>44</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15" thickBot="1">
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>46</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="29.45" thickBot="1">
+    <row r="25" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>48</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="29.45" thickBot="1">
+    <row r="26" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>50</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="29.45" thickBot="1">
+    <row r="27" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="29.45" thickBot="1">
+    <row r="28" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16" t="s">
         <v>54</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="29.45" thickBot="1">
+    <row r="29" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16" t="s">
         <v>56</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15" thickBot="1">
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16" t="s">
         <v>58</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="29.45" thickBot="1">
+    <row r="31" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16" t="s">
         <v>60</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15" thickBot="1">
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16" t="s">
         <v>62</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="29.45" thickBot="1">
+    <row r="33" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16" t="s">
         <v>64</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="29.45" thickBot="1">
+    <row r="34" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16" t="s">
         <v>66</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15" thickBot="1">
+    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16" t="s">
         <v>68</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15" thickBot="1">
+    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16" t="s">
         <v>70</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" thickBot="1">
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16" t="s">
         <v>72</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="18.600000000000001">
+    <row r="38" spans="1:2" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
     </row>
   </sheetData>
@@ -1927,13 +1927,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6220684-BCCE-4AEA-919F-82946927E7EC}">
   <dimension ref="A1:B187"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
-    <col min="2" max="2" width="71.5703125" customWidth="1"/>
+    <col min="2" max="2" width="71.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>74</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21" t="s">
         <v>76</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="4" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21" t="s">
         <v>78</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21" t="s">
         <v>80</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21" t="s">
         <v>82</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="67.5" customHeight="1">
+    <row r="7" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>84</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="8" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21" t="s">
         <v>86</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="9" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21" t="s">
         <v>88</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="10" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21" t="s">
         <v>90</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="11" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21" t="s">
         <v>92</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="12" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21" t="s">
         <v>94</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="13" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21" t="s">
         <v>95</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="14" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21" t="s">
         <v>96</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="15" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21" t="s">
         <v>97</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21" t="s">
         <v>98</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="17" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="21" t="s">
         <v>100</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="18" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="21" t="s">
         <v>102</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="67.5" customHeight="1" thickBot="1">
+    <row r="19" spans="1:2" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="21" t="s">
         <v>104</v>
       </c>
@@ -2085,174 +2085,174 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="21" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="22" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="23" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="24" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="25" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="26" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="27" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="28" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="29" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="30" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="31" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="32" spans="1:2" ht="67.5" customHeight="1"/>
-    <row r="33" ht="67.5" customHeight="1"/>
-    <row r="34" ht="67.5" customHeight="1"/>
-    <row r="35" ht="67.5" customHeight="1"/>
-    <row r="36" ht="67.5" customHeight="1"/>
-    <row r="37" ht="67.5" customHeight="1"/>
-    <row r="38" ht="67.5" customHeight="1"/>
-    <row r="39" ht="67.5" customHeight="1"/>
-    <row r="40" ht="67.5" customHeight="1"/>
-    <row r="41" ht="67.5" customHeight="1"/>
-    <row r="42" ht="67.5" customHeight="1"/>
-    <row r="43" ht="67.5" customHeight="1"/>
-    <row r="44" ht="67.5" customHeight="1"/>
-    <row r="45" ht="67.5" customHeight="1"/>
-    <row r="46" ht="67.5" customHeight="1"/>
-    <row r="47" ht="67.5" customHeight="1"/>
-    <row r="48" ht="67.5" customHeight="1"/>
-    <row r="49" ht="67.5" customHeight="1"/>
-    <row r="50" ht="67.5" customHeight="1"/>
-    <row r="51" ht="67.5" customHeight="1"/>
-    <row r="52" ht="67.5" customHeight="1"/>
-    <row r="53" ht="67.5" customHeight="1"/>
-    <row r="54" ht="67.5" customHeight="1"/>
-    <row r="55" ht="67.5" customHeight="1"/>
-    <row r="56" ht="67.5" customHeight="1"/>
-    <row r="57" ht="67.5" customHeight="1"/>
-    <row r="58" ht="67.5" customHeight="1"/>
-    <row r="59" ht="67.5" customHeight="1"/>
-    <row r="60" ht="67.5" customHeight="1"/>
-    <row r="61" ht="67.5" customHeight="1"/>
-    <row r="62" ht="67.5" customHeight="1"/>
-    <row r="63" ht="67.5" customHeight="1"/>
-    <row r="64" ht="67.5" customHeight="1"/>
-    <row r="65" ht="67.5" customHeight="1"/>
-    <row r="66" ht="67.5" customHeight="1"/>
-    <row r="67" ht="67.5" customHeight="1"/>
-    <row r="68" ht="67.5" customHeight="1"/>
-    <row r="69" ht="67.5" customHeight="1"/>
-    <row r="70" ht="67.5" customHeight="1"/>
-    <row r="71" ht="67.5" customHeight="1"/>
-    <row r="72" ht="67.5" customHeight="1"/>
-    <row r="73" ht="67.5" customHeight="1"/>
-    <row r="74" ht="67.5" customHeight="1"/>
-    <row r="75" ht="67.5" customHeight="1"/>
-    <row r="76" ht="67.5" customHeight="1"/>
-    <row r="77" ht="67.5" customHeight="1"/>
-    <row r="78" ht="67.5" customHeight="1"/>
-    <row r="79" ht="67.5" customHeight="1"/>
-    <row r="80" ht="67.5" customHeight="1"/>
-    <row r="81" ht="67.5" customHeight="1"/>
-    <row r="82" ht="67.5" customHeight="1"/>
-    <row r="83" ht="67.5" customHeight="1"/>
-    <row r="84" ht="67.5" customHeight="1"/>
-    <row r="85" ht="67.5" customHeight="1"/>
-    <row r="86" ht="67.5" customHeight="1"/>
-    <row r="87" ht="67.5" customHeight="1"/>
-    <row r="88" ht="67.5" customHeight="1"/>
-    <row r="89" ht="67.5" customHeight="1"/>
-    <row r="90" ht="67.5" customHeight="1"/>
-    <row r="91" ht="67.5" customHeight="1"/>
-    <row r="92" ht="67.5" customHeight="1"/>
-    <row r="93" ht="67.5" customHeight="1"/>
-    <row r="94" ht="67.5" customHeight="1"/>
-    <row r="95" ht="67.5" customHeight="1"/>
-    <row r="96" ht="67.5" customHeight="1"/>
-    <row r="97" ht="67.5" customHeight="1"/>
-    <row r="98" ht="67.5" customHeight="1"/>
-    <row r="99" ht="67.5" customHeight="1"/>
-    <row r="100" ht="67.5" customHeight="1"/>
-    <row r="101" ht="67.5" customHeight="1"/>
-    <row r="102" ht="67.5" customHeight="1"/>
-    <row r="103" ht="67.5" customHeight="1"/>
-    <row r="104" ht="67.5" customHeight="1"/>
-    <row r="105" ht="67.5" customHeight="1"/>
-    <row r="106" ht="67.5" customHeight="1"/>
-    <row r="107" ht="67.5" customHeight="1"/>
-    <row r="108" ht="67.5" customHeight="1"/>
-    <row r="109" ht="67.5" customHeight="1"/>
-    <row r="110" ht="67.5" customHeight="1"/>
-    <row r="111" ht="67.5" customHeight="1"/>
-    <row r="112" ht="67.5" customHeight="1"/>
-    <row r="113" ht="67.5" customHeight="1"/>
-    <row r="114" ht="67.5" customHeight="1"/>
-    <row r="115" ht="67.5" customHeight="1"/>
-    <row r="116" ht="67.5" customHeight="1"/>
-    <row r="117" ht="67.5" customHeight="1"/>
-    <row r="118" ht="67.5" customHeight="1"/>
-    <row r="119" ht="67.5" customHeight="1"/>
-    <row r="120" ht="67.5" customHeight="1"/>
-    <row r="121" ht="67.5" customHeight="1"/>
-    <row r="122" ht="67.5" customHeight="1"/>
-    <row r="123" ht="67.5" customHeight="1"/>
-    <row r="124" ht="67.5" customHeight="1"/>
-    <row r="125" ht="67.5" customHeight="1"/>
-    <row r="126" ht="67.5" customHeight="1"/>
-    <row r="127" ht="67.5" customHeight="1"/>
-    <row r="128" ht="67.5" customHeight="1"/>
-    <row r="129" ht="67.5" customHeight="1"/>
-    <row r="130" ht="67.5" customHeight="1"/>
-    <row r="131" ht="67.5" customHeight="1"/>
-    <row r="132" ht="67.5" customHeight="1"/>
-    <row r="133" ht="67.5" customHeight="1"/>
-    <row r="134" ht="67.5" customHeight="1"/>
-    <row r="135" ht="67.5" customHeight="1"/>
-    <row r="136" ht="67.5" customHeight="1"/>
-    <row r="137" ht="67.5" customHeight="1"/>
-    <row r="138" ht="67.5" customHeight="1"/>
-    <row r="139" ht="67.5" customHeight="1"/>
-    <row r="140" ht="67.5" customHeight="1"/>
-    <row r="141" ht="67.5" customHeight="1"/>
-    <row r="142" ht="67.5" customHeight="1"/>
-    <row r="143" ht="67.5" customHeight="1"/>
-    <row r="144" ht="67.5" customHeight="1"/>
-    <row r="145" ht="67.5" customHeight="1"/>
-    <row r="146" ht="67.5" customHeight="1"/>
-    <row r="147" ht="67.5" customHeight="1"/>
-    <row r="148" ht="67.5" customHeight="1"/>
-    <row r="149" ht="67.5" customHeight="1"/>
-    <row r="150" ht="67.5" customHeight="1"/>
-    <row r="151" ht="67.5" customHeight="1"/>
-    <row r="152" ht="67.5" customHeight="1"/>
-    <row r="153" ht="67.5" customHeight="1"/>
-    <row r="154" ht="67.5" customHeight="1"/>
-    <row r="155" ht="67.5" customHeight="1"/>
-    <row r="156" ht="67.5" customHeight="1"/>
-    <row r="157" ht="67.5" customHeight="1"/>
-    <row r="158" ht="67.5" customHeight="1"/>
-    <row r="159" ht="67.5" customHeight="1"/>
-    <row r="160" ht="67.5" customHeight="1"/>
-    <row r="161" ht="67.5" customHeight="1"/>
-    <row r="162" ht="67.5" customHeight="1"/>
-    <row r="163" ht="67.5" customHeight="1"/>
-    <row r="164" ht="67.5" customHeight="1"/>
-    <row r="165" ht="67.5" customHeight="1"/>
-    <row r="166" ht="67.5" customHeight="1"/>
-    <row r="167" ht="67.5" customHeight="1"/>
-    <row r="168" ht="67.5" customHeight="1"/>
-    <row r="169" ht="67.5" customHeight="1"/>
-    <row r="170" ht="67.5" customHeight="1"/>
-    <row r="171" ht="67.5" customHeight="1"/>
-    <row r="172" ht="67.5" customHeight="1"/>
-    <row r="173" ht="67.5" customHeight="1"/>
-    <row r="174" ht="67.5" customHeight="1"/>
-    <row r="175" ht="67.5" customHeight="1"/>
-    <row r="176" ht="67.5" customHeight="1"/>
-    <row r="177" ht="67.5" customHeight="1"/>
-    <row r="178" ht="67.5" customHeight="1"/>
-    <row r="179" ht="67.5" customHeight="1"/>
-    <row r="180" ht="67.5" customHeight="1"/>
-    <row r="181" ht="67.5" customHeight="1"/>
-    <row r="182" ht="67.5" customHeight="1"/>
-    <row r="183" ht="67.5" customHeight="1"/>
-    <row r="184" ht="67.5" customHeight="1"/>
-    <row r="185" ht="67.5" customHeight="1"/>
-    <row r="186" ht="67.5" customHeight="1"/>
-    <row r="187" ht="67.5" customHeight="1"/>
+    <row r="20" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="34" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="36" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="37" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="38" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="115" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="116" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="117" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="118" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="120" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="121" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="122" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="123" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="124" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="125" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="128" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="130" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="131" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="132" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="133" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="134" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="136" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="137" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="138" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="140" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="141" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="142" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="143" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="144" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="67.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2261,13 +2261,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538DCCDF-A36C-4D66-810A-58593C628C13}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="90.140625" customWidth="1"/>
-    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="1" max="1" width="90.1796875" customWidth="1"/>
+    <col min="2" max="2" width="110.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="1" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="2" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>106</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="3" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>108</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="4" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>110</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="5" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>112</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="6" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>114</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="7" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>116</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="8" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>118</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="9" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>120</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="41.1" customHeight="1" thickBot="1">
+    <row r="10" spans="1:2" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>122</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>124</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>126</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>128</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="14" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>130</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="15" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
         <v>132</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="16" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>134</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="17" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>136</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>138</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="19" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>140</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="20" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>142</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="21" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>144</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="22" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
         <v>146</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="23" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
         <v>148</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="24" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>150</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="25" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
         <v>152</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="26" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>154</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="47.45" customHeight="1" thickBot="1">
+    <row r="27" spans="1:2" ht="47.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>156</v>
       </c>
@@ -2491,14 +2491,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1579D4-A75A-44F4-8306-7E5430B3C965}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" customWidth="1"/>
-    <col min="2" max="2" width="90.5703125" customWidth="1"/>
+    <col min="1" max="1" width="70.453125" customWidth="1"/>
+    <col min="2" max="2" width="90.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1"/>
-    <row r="2" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="1" spans="1:2" ht="35" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>158</v>
       </c>
@@ -2506,7 +2513,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>160</v>
       </c>
@@ -2514,7 +2521,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="4" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>162</v>
       </c>
@@ -2522,7 +2529,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>164</v>
       </c>
@@ -2530,7 +2537,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>166</v>
       </c>
@@ -2538,7 +2545,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="7" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>168</v>
       </c>
@@ -2546,7 +2553,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="8" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>170</v>
       </c>
@@ -2554,7 +2561,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="9" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>172</v>
       </c>
@@ -2562,7 +2569,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="10" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>174</v>
       </c>
@@ -2570,7 +2577,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="40.5" customHeight="1">
+    <row r="11" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>176</v>
       </c>
@@ -2578,7 +2585,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="12" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
         <v>178</v>
       </c>
@@ -2586,7 +2593,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="40.5" customHeight="1">
+    <row r="13" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27" t="s">
         <v>180</v>
       </c>
@@ -2594,19 +2601,19 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="40.5" customHeight="1">
+    <row r="14" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="28"/>
       <c r="B14" s="6" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="15" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="29"/>
       <c r="B15" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>184</v>
       </c>
@@ -2614,7 +2621,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="17" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>186</v>
       </c>
@@ -2622,7 +2629,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="18" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>188</v>
       </c>
@@ -2630,7 +2637,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="19" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>190</v>
       </c>
@@ -2638,7 +2645,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="20" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>192</v>
       </c>
@@ -2646,7 +2653,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="21" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>194</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="22" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
         <v>196</v>
       </c>
@@ -2662,7 +2669,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="23" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
         <v>198</v>
       </c>
@@ -2670,7 +2677,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="24" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>200</v>
       </c>
@@ -2678,7 +2685,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="25" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
         <v>202</v>
       </c>
@@ -2686,7 +2693,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="26" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>204</v>
       </c>
@@ -2694,7 +2701,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="27" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>206</v>
       </c>
@@ -2702,7 +2709,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="28" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
         <v>208</v>
       </c>
@@ -2710,7 +2717,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="40.5" customHeight="1" thickBot="1">
+    <row r="29" spans="1:2" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
         <v>210</v>
       </c>
@@ -2718,8 +2725,8 @@
         <v>211</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="40.5" customHeight="1"/>
-    <row r="31" spans="1:2" ht="40.5" customHeight="1"/>
+    <row r="30" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A13:A15"/>
@@ -2731,13 +2738,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64221CC5-6653-40F9-9E75-F5B728A8F499}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" customWidth="1"/>
-    <col min="2" max="2" width="49.42578125" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" customWidth="1"/>
+    <col min="2" max="2" width="49.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="35.1" thickBot="1">
+    <row r="1" spans="1:2" ht="35" thickBot="1" x14ac:dyDescent="0.85">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2745,7 +2752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="2" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>212</v>
       </c>
@@ -2753,7 +2760,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="3" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>214</v>
       </c>
@@ -2761,7 +2768,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="4" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>216</v>
       </c>
@@ -2769,7 +2776,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="50.45" customHeight="1">
+    <row r="5" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>218</v>
       </c>
@@ -2777,13 +2784,13 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="6" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
         <v>220</v>
       </c>
       <c r="B6" s="29"/>
     </row>
-    <row r="7" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="7" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>221</v>
       </c>
@@ -2791,7 +2798,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="8" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>223</v>
       </c>
@@ -2799,7 +2806,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="9" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>225</v>
       </c>
@@ -2807,7 +2814,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="10" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>227</v>
       </c>
@@ -2815,7 +2822,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>229</v>
       </c>
@@ -2823,7 +2830,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>231</v>
       </c>
@@ -2831,13 +2838,13 @@
         <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>233</v>
       </c>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="14" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>234</v>
       </c>
@@ -2845,7 +2852,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="15" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>236</v>
       </c>
@@ -2853,7 +2860,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="16" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>238</v>
       </c>
@@ -2861,7 +2868,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="17" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>240</v>
       </c>
@@ -2869,7 +2876,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>242</v>
       </c>
@@ -2877,28 +2884,28 @@
         <v>243</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="50.45" customHeight="1">
+    <row r="19" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="27" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="50.45" customHeight="1" thickBot="1">
+    <row r="20" spans="1:2" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>245</v>
       </c>
       <c r="B20" s="29"/>
     </row>
-    <row r="21" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="22" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="23" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="24" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="25" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="26" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="27" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="28" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="29" spans="1:2" ht="50.45" customHeight="1"/>
-    <row r="30" spans="1:2" ht="50.45" customHeight="1"/>
+    <row r="21" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:2" ht="50.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B5:B6"/>
@@ -2911,13 +2918,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00C0E5A-777E-4FD4-A6AF-203CF6830405}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="1" max="1" width="50.81640625" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2925,7 +2932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>246</v>
       </c>
@@ -2933,7 +2940,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>248</v>
       </c>
@@ -2941,7 +2948,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="4" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>250</v>
       </c>
@@ -2949,7 +2956,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>252</v>
       </c>
@@ -2957,7 +2964,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>254</v>
       </c>
@@ -2965,7 +2972,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="7" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>256</v>
       </c>
@@ -2973,7 +2980,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="8" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>258</v>
       </c>
@@ -2981,7 +2988,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="9" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>260</v>
       </c>
@@ -2989,7 +2996,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="34.5" customHeight="1">
+    <row r="10" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>262</v>
       </c>
@@ -2997,13 +3004,13 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="11" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
         <v>220</v>
       </c>
       <c r="B11" s="29"/>
     </row>
-    <row r="12" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="12" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>264</v>
       </c>
@@ -3011,7 +3018,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="13" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>266</v>
       </c>
@@ -3019,7 +3026,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="14" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>268</v>
       </c>
@@ -3027,7 +3034,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="15" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>270</v>
       </c>
@@ -3035,7 +3042,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>272</v>
       </c>
@@ -3043,7 +3050,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="34.5" customHeight="1">
+    <row r="17" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>274</v>
       </c>
@@ -3051,7 +3058,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="18" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>276</v>
       </c>
@@ -3059,7 +3066,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="19" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>278</v>
       </c>
@@ -3067,7 +3074,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="20" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>280</v>
       </c>
@@ -3075,7 +3082,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="21" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>282</v>
       </c>
@@ -3083,7 +3090,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="34.5" customHeight="1" thickBot="1">
+    <row r="22" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
         <v>284</v>
       </c>
